--- a/academias/Programación - Estadisticos 20232.xlsx
+++ b/academias/Programación - Estadisticos 20232.xlsx
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1439,25 +1439,25 @@
         <v>15</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>6.7</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1471,25 +1471,25 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>11.1</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1506,25 +1506,25 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>12.9</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1541,25 +1541,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>16.1</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1576,25 +1576,25 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>78.3</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>21.7</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1608,25 +1608,25 @@
         <v>85</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="F8">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>83.5</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>16.5</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1643,25 +1643,25 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>11.4</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1678,25 +1678,25 @@
         <v>21</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>4.8</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J10">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1710,25 +1710,25 @@
         <v>56</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F11">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>8.9</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1745,25 +1745,25 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1780,25 +1780,25 @@
         <v>24</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F13">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1812,25 +1812,25 @@
         <v>59</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F14">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>11.9</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J14">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1847,25 +1847,25 @@
         <v>15</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F15">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>6.7</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J15">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1879,25 +1879,25 @@
         <v>15</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F16">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>6.7</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J16">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1914,25 +1914,25 @@
         <v>31</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F17">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>19.4</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J17">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J18">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1984,25 +1984,25 @@
         <v>24</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F19">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>95.8</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>4.2</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J19">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2016,25 +2016,25 @@
         <v>90</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="F20">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>15.6</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J20">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2051,25 +2051,25 @@
         <v>23</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F21">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J21">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2086,25 +2086,25 @@
         <v>23</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F22">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>4.3</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J22">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2121,25 +2121,25 @@
         <v>21</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F23">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>76.2</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>23.8</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J23">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2153,25 +2153,25 @@
         <v>67</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F24">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>11.9</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J24">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2182,25 +2182,25 @@
         <v>408</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="F25">
-        <v>408</v>
+        <v>53</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J25">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2268,19 +2268,19 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>90.5</v>
+        <v>85.7</v>
       </c>
       <c r="H2" s="1">
-        <v>9.5</v>
+        <v>14.3</v>
       </c>
       <c r="I2" s="2">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>6.7</v>
       </c>
       <c r="I3" s="2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2335,19 +2335,19 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>91.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>8.300000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>83.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>16.1</v>
+        <v>12.9</v>
       </c>
       <c r="I5" s="2">
         <v>7.1</v>
@@ -2405,16 +2405,16 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>87.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>12.9</v>
+        <v>16.1</v>
       </c>
       <c r="I6" s="2">
         <v>7.2</v>
@@ -2440,19 +2440,19 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>65.2</v>
+        <v>78.3</v>
       </c>
       <c r="H7" s="1">
-        <v>34.8</v>
+        <v>21.7</v>
       </c>
       <c r="I7" s="2">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2472,19 +2472,19 @@
         <v>85</v>
       </c>
       <c r="E8">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1">
-        <v>80</v>
+        <v>83.5</v>
       </c>
       <c r="H8" s="1">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="I8" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2507,19 +2507,19 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>85.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>14.3</v>
+        <v>11.4</v>
       </c>
       <c r="I9" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2542,19 +2542,19 @@
         <v>21</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>90.5</v>
+        <v>95.2</v>
       </c>
       <c r="H10" s="1">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="I10" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2574,19 +2574,19 @@
         <v>56</v>
       </c>
       <c r="E11">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>87.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>12.5</v>
+        <v>8.9</v>
       </c>
       <c r="I11" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2609,19 +2609,19 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>91.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H12" s="1">
-        <v>8.6</v>
+        <v>14.3</v>
       </c>
       <c r="I12" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2656,7 +2656,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I13" s="2">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2676,19 +2676,19 @@
         <v>59</v>
       </c>
       <c r="E14">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>91.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>8.5</v>
+        <v>11.9</v>
       </c>
       <c r="I14" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2723,7 +2723,7 @@
         <v>6.7</v>
       </c>
       <c r="I15" s="2">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2755,7 +2755,7 @@
         <v>6.7</v>
       </c>
       <c r="I16" s="2">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2778,19 +2778,19 @@
         <v>31</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F17">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>64.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>35.5</v>
+        <v>19.4</v>
       </c>
       <c r="I17" s="2">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2825,7 +2825,7 @@
         <v>20</v>
       </c>
       <c r="I18" s="2">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2848,19 +2848,19 @@
         <v>24</v>
       </c>
       <c r="E19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H19" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I19" s="2">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2880,19 +2880,19 @@
         <v>90</v>
       </c>
       <c r="E20">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G20" s="1">
-        <v>77.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="I20" s="2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2927,7 +2927,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="I21" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2950,19 +2950,19 @@
         <v>23</v>
       </c>
       <c r="E22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>91.3</v>
+        <v>95.7</v>
       </c>
       <c r="H22" s="1">
-        <v>8.699999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="I22" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2985,19 +2985,19 @@
         <v>21</v>
       </c>
       <c r="E23">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F23">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
-        <v>57.1</v>
+        <v>76.2</v>
       </c>
       <c r="H23" s="1">
-        <v>42.9</v>
+        <v>23.8</v>
       </c>
       <c r="I23" s="2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3017,19 +3017,19 @@
         <v>67</v>
       </c>
       <c r="E24">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F24">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G24" s="1">
-        <v>80.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H24" s="1">
-        <v>19.4</v>
+        <v>11.9</v>
       </c>
       <c r="I24" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3046,19 +3046,19 @@
         <v>408</v>
       </c>
       <c r="E25">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="F25">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="G25" s="1">
-        <v>83.8</v>
+        <v>87</v>
       </c>
       <c r="H25" s="1">
-        <v>16.2</v>
+        <v>13</v>
       </c>
       <c r="I25" s="2">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J25">
         <v>0</v>

--- a/academias/Programación - Estadisticos 20232.xlsx
+++ b/academias/Programación - Estadisticos 20232.xlsx
@@ -2268,16 +2268,16 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>85.7</v>
+        <v>90.5</v>
       </c>
       <c r="H2" s="1">
-        <v>14.3</v>
+        <v>9.5</v>
       </c>
       <c r="I2" s="2">
         <v>7.5</v>
@@ -2315,7 +2315,7 @@
         <v>6.7</v>
       </c>
       <c r="I3" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2335,16 +2335,16 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>88.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="H4" s="1">
-        <v>11.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4" s="2">
         <v>7.8</v>
@@ -2370,19 +2370,19 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>87.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="H5" s="1">
-        <v>12.9</v>
+        <v>6.5</v>
       </c>
       <c r="I5" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2405,16 +2405,16 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>83.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="H6" s="1">
-        <v>16.1</v>
+        <v>3.2</v>
       </c>
       <c r="I6" s="2">
         <v>7.2</v>
@@ -2440,19 +2440,19 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>78.3</v>
+        <v>95.7</v>
       </c>
       <c r="H7" s="1">
-        <v>21.7</v>
+        <v>4.3</v>
       </c>
       <c r="I7" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2472,19 +2472,19 @@
         <v>85</v>
       </c>
       <c r="E8">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>83.5</v>
+        <v>95.3</v>
       </c>
       <c r="H8" s="1">
-        <v>16.5</v>
+        <v>4.7</v>
       </c>
       <c r="I8" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2507,19 +2507,19 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>88.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>11.4</v>
+        <v>8.6</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2542,19 +2542,19 @@
         <v>21</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>95.2</v>
+        <v>85.7</v>
       </c>
       <c r="H10" s="1">
-        <v>4.8</v>
+        <v>14.3</v>
       </c>
       <c r="I10" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2574,19 +2574,19 @@
         <v>56</v>
       </c>
       <c r="E11">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>91.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="H11" s="1">
-        <v>8.9</v>
+        <v>10.7</v>
       </c>
       <c r="I11" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2609,19 +2609,19 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>85.7</v>
+        <v>94.3</v>
       </c>
       <c r="H12" s="1">
-        <v>14.3</v>
+        <v>5.7</v>
       </c>
       <c r="I12" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2644,16 +2644,16 @@
         <v>24</v>
       </c>
       <c r="E13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H13" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I13" s="2">
         <v>8</v>
@@ -2676,19 +2676,19 @@
         <v>59</v>
       </c>
       <c r="E14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>88.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>11.9</v>
+        <v>5.1</v>
       </c>
       <c r="I14" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2778,19 +2778,19 @@
         <v>31</v>
       </c>
       <c r="E17">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>80.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="H17" s="1">
-        <v>19.4</v>
+        <v>6.5</v>
       </c>
       <c r="I17" s="2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2813,16 +2813,16 @@
         <v>35</v>
       </c>
       <c r="E18">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>80</v>
+        <v>94.3</v>
       </c>
       <c r="H18" s="1">
-        <v>20</v>
+        <v>5.7</v>
       </c>
       <c r="I18" s="2">
         <v>7.7</v>
@@ -2860,7 +2860,7 @@
         <v>4.2</v>
       </c>
       <c r="I19" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2880,19 +2880,19 @@
         <v>90</v>
       </c>
       <c r="E20">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F20">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1">
-        <v>84.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>15.6</v>
+        <v>5.6</v>
       </c>
       <c r="I20" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2915,19 +2915,19 @@
         <v>23</v>
       </c>
       <c r="E21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>91.3</v>
+        <v>95.7</v>
       </c>
       <c r="H21" s="1">
-        <v>8.699999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="I21" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2962,7 +2962,7 @@
         <v>4.3</v>
       </c>
       <c r="I22" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2985,16 +2985,16 @@
         <v>21</v>
       </c>
       <c r="E23">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G23" s="1">
-        <v>76.2</v>
+        <v>90.5</v>
       </c>
       <c r="H23" s="1">
-        <v>23.8</v>
+        <v>9.5</v>
       </c>
       <c r="I23" s="2">
         <v>7.3</v>
@@ -3017,19 +3017,19 @@
         <v>67</v>
       </c>
       <c r="E24">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G24" s="1">
-        <v>88.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="H24" s="1">
-        <v>11.9</v>
+        <v>6</v>
       </c>
       <c r="I24" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3046,16 +3046,16 @@
         <v>408</v>
       </c>
       <c r="E25">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="F25">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G25" s="1">
-        <v>87</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H25" s="1">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="I25" s="2">
         <v>7.7</v>
